--- a/src/assets/formats/print/magazine/Magazine.xlsx
+++ b/src/assets/formats/print/magazine/Magazine.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5febf3aab2d16ef7/Desktop/New Proposals/Print/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Backend plan generator\src\assets\formats\print\magazine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="149" documentId="13_ncr:1_{BC78FE97-0C6A-42D8-814F-76F490EA037D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7100AE7-C4D0-451A-A312-754F5714D1C7}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E757FF19-7DC8-4A90-A7C3-AC38EF403258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{A47B5068-0EA7-46C4-894F-84D1B6A7E8D3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{A47B5068-0EA7-46C4-894F-84D1B6A7E8D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Magazine" sheetId="1" r:id="rId1"/>
@@ -37,8 +37,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>Proposal for Magazine Advertising</t>
   </si>
@@ -109,9 +131,6 @@
     <t>Result</t>
   </si>
   <si>
-    <t>Picture</t>
-  </si>
-  <si>
     <t>Magazine advertising builds authority and aspiration by placing your brand within curated, high-trust editorial environments consumed by premium audiences.</t>
   </si>
   <si>
@@ -126,15 +145,30 @@
   <si>
     <t xml:space="preserve">The next evolution of adtech infrastructure and a unified command center that brings digital-level precision to every channel, both online and offline. Through a single, integrated dashboard, brands can plan, execute, and evaluate campaigns across all services, locations, and companies in one place, while gaining full transparency, real-time tracking, and performance visibility even for traditionally offline media. </t>
   </si>
+  <si>
+    <t>Rio Luxury Homes</t>
+  </si>
+  <si>
+    <t>To build awareness and position the brand as a premium, aspirational housing choice.</t>
+  </si>
+  <si>
+    <t>Advertised in premium print magazines with visually appealing creatives targeting high-end audiences.</t>
+  </si>
+  <si>
+    <t>Improved brand visibility, stronger premium perception, and increased customer inquiries.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="168" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -211,6 +245,50 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -238,7 +316,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -337,10 +415,25 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right/>
       <top/>
-      <bottom style="thin">
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -349,19 +442,168 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right/>
-      <top/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
@@ -377,6 +619,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -399,45 +644,145 @@
     <xf numFmtId="3" fontId="7" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="17" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="18" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="16" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="24" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="24" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="24" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="24" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="24" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="24" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="24" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="24" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="24" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="24" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="24" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="24" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="24" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="24" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="4" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="31">
     <cellStyle name="Comma 2" xfId="1" xr:uid="{43A4675C-1B1D-403B-81F3-AC58F4A77479}"/>
     <cellStyle name="Comma 2 2" xfId="3" xr:uid="{E249453A-A332-40F0-A2DA-AD38129FE20B}"/>
+    <cellStyle name="Comma 2 2 2" xfId="23" xr:uid="{BE8B6B5D-4963-4A49-8C0A-30E115610A62}"/>
+    <cellStyle name="Comma 2 2 3" xfId="28" xr:uid="{1C151718-D5C7-4E59-B3D8-FB6ECFC30617}"/>
+    <cellStyle name="Comma 2 2 4" xfId="19" xr:uid="{8486F36E-B0B8-45CC-904E-9C713E05AD50}"/>
+    <cellStyle name="Comma 2 3" xfId="21" xr:uid="{A3DC3F37-E8B3-4EEE-A2F4-C6EACA00F7C2}"/>
+    <cellStyle name="Comma 2 4" xfId="26" xr:uid="{D72A303C-559A-4FB5-A9A7-775D809986E2}"/>
+    <cellStyle name="Comma 2 5" xfId="7" xr:uid="{36BE6A8A-A893-4C68-AAA3-FC78A28763F1}"/>
+    <cellStyle name="Excel Built-in Normal" xfId="10" xr:uid="{1D3A5408-EED5-4899-915F-E64CBA3E2C34}"/>
+    <cellStyle name="Hyperlink 2" xfId="11" xr:uid="{06E064BE-5FBE-43AD-9746-E8A695AF64EA}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 10" xfId="24" xr:uid="{D9712960-243E-405D-96BA-BC4C51613249}"/>
+    <cellStyle name="Normal 11" xfId="30" xr:uid="{652198C0-B37A-4B3E-83B1-9C300FA2C7B8}"/>
+    <cellStyle name="Normal 12" xfId="4" xr:uid="{F953F2A1-3B14-4DAC-8361-E339473C0824}"/>
+    <cellStyle name="Normal 19 2" xfId="15" xr:uid="{F350EC99-F182-4BFF-8DEF-8EE27B79FF77}"/>
+    <cellStyle name="Normal 2" xfId="9" xr:uid="{03893673-44D6-48BF-BB79-552A746C42D2}"/>
+    <cellStyle name="Normal 2 10" xfId="8" xr:uid="{8A04A401-F783-4E25-BCFB-70122CF8DCFB}"/>
+    <cellStyle name="Normal 2 2 2" xfId="6" xr:uid="{F5D80B4B-626E-481F-B287-2D087A43DC4E}"/>
+    <cellStyle name="Normal 2_Copy of Digjam 2009-10 Budget" xfId="5" xr:uid="{04569A69-5196-44B8-BE6A-3B7481361B29}"/>
+    <cellStyle name="Normal 3" xfId="12" xr:uid="{D575B1F7-06EC-41DC-B251-DB6D43C2477C}"/>
+    <cellStyle name="Normal 3 2" xfId="13" xr:uid="{92AA236B-198D-4C2A-8F7A-AE282BF30CF6}"/>
+    <cellStyle name="Normal 4" xfId="16" xr:uid="{5A2AFE94-2F54-4726-8739-C1C4B42E64C8}"/>
+    <cellStyle name="Normal 5" xfId="17" xr:uid="{5BE6F10B-6659-4002-9423-36444580B110}"/>
     <cellStyle name="Normal 6" xfId="2" xr:uid="{662DA933-11C1-403F-9BE9-E937AADB8AB0}"/>
+    <cellStyle name="Normal 6 2" xfId="20" xr:uid="{2718863B-DD2A-4FCD-9BF3-094CAB88B2C1}"/>
+    <cellStyle name="Normal 6 3" xfId="27" xr:uid="{DA3A6503-19E0-4C66-A38D-DAEF63847984}"/>
+    <cellStyle name="Normal 7" xfId="18" xr:uid="{F96CC72A-5763-4D06-BC68-796CEC9EF072}"/>
+    <cellStyle name="Normal 7 2" xfId="22" xr:uid="{8E06BE6E-1466-4C03-B806-53CD6C581A5D}"/>
+    <cellStyle name="Normal 8" xfId="25" xr:uid="{379E1146-F761-4640-9CB9-0A4BFE8370D4}"/>
+    <cellStyle name="Normal 8 2" xfId="14" xr:uid="{6241778E-CE2F-4B0A-9CBF-0970FF08B66C}"/>
+    <cellStyle name="Normal 9" xfId="29" xr:uid="{7FC89BEB-4744-4854-8098-F82B4F6B4EFB}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -16291,8 +16636,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7509933" y="1062323"/>
-          <a:ext cx="7158567" cy="4441982"/>
+          <a:off x="7509933" y="1049623"/>
+          <a:ext cx="7178887" cy="4473732"/>
           <a:chOff x="7113693" y="1069943"/>
           <a:chExt cx="7105541" cy="4441982"/>
         </a:xfrm>
@@ -16413,8 +16758,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="152400" y="1059181"/>
-          <a:ext cx="7170420" cy="4450939"/>
+          <a:off x="152400" y="1046481"/>
+          <a:ext cx="7170420" cy="4482689"/>
           <a:chOff x="0" y="1066801"/>
           <a:chExt cx="7063740" cy="4450939"/>
         </a:xfrm>
@@ -16512,8 +16857,68 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -16834,20 +17239,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8710BEBA-4AB7-48BE-8C3F-450C42133126}">
   <dimension ref="A1:K24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="11.6640625" customWidth="1"/>
-    <col min="4" max="4" width="26.44140625" customWidth="1"/>
-    <col min="5" max="5" width="13.5546875" customWidth="1"/>
-    <col min="6" max="6" width="13.88671875" customWidth="1"/>
-    <col min="7" max="7" width="17.33203125" customWidth="1"/>
+    <col min="2" max="2" width="11.6328125" customWidth="1"/>
+    <col min="4" max="4" width="26.453125" customWidth="1"/>
+    <col min="5" max="5" width="13.54296875" customWidth="1"/>
+    <col min="6" max="6" width="13.90625" customWidth="1"/>
+    <col min="7" max="7" width="17.36328125" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="20.33203125" customWidth="1"/>
-    <col min="10" max="10" width="13.88671875" customWidth="1"/>
-    <col min="11" max="11" width="15.21875" customWidth="1"/>
+    <col min="9" max="9" width="20.36328125" customWidth="1"/>
+    <col min="10" max="10" width="13.90625" customWidth="1"/>
+    <col min="11" max="11" width="15.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -16860,7 +17265,7 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -16873,7 +17278,7 @@
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" spans="1:11" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="29.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -16886,7 +17291,7 @@
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="1:11" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="40.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -16899,7 +17304,7 @@
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
     </row>
-    <row r="5" spans="1:11" ht="44.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" ht="44.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -16912,22 +17317,22 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
     </row>
-    <row r="6" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="10" t="s">
+    <row r="6" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="12"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="13"/>
     </row>
-    <row r="7" spans="1:11" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="31.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>1</v>
       </c>
@@ -16962,7 +17367,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -16975,7 +17380,7 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -16988,7 +17393,7 @@
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -17001,7 +17406,7 @@
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -17014,7 +17419,7 @@
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -17027,7 +17432,7 @@
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -17040,7 +17445,7 @@
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -17053,7 +17458,7 @@
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -17066,7 +17471,7 @@
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -17079,7 +17484,7 @@
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -17092,110 +17497,110 @@
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
     </row>
-    <row r="18" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="13" t="s">
+    <row r="18" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
     </row>
-    <row r="19" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="14" t="s">
+    <row r="19" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="14"/>
-      <c r="K19" s="14"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
     </row>
-    <row r="20" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="14" t="s">
+    <row r="20" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
     </row>
-    <row r="21" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
+    <row r="21" spans="1:11" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
     </row>
-    <row r="22" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
+    <row r="22" spans="1:11" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="8"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
     </row>
-    <row r="23" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
+    <row r="23" spans="1:11" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="8"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="9" t="s">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A24" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -17216,501 +17621,537 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDC6FCAF-99B7-4066-A34B-4A8B9E3B9C8C}">
   <dimension ref="B1:M35"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="2:13" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="20" t="s">
+    <row r="1" spans="2:13" ht="31.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="36"/>
+    </row>
+    <row r="2" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B2" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="39" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="40"/>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B3" s="43" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="40"/>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B4" s="43"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="39"/>
+      <c r="K4" s="39"/>
+      <c r="L4" s="39"/>
+      <c r="M4" s="40"/>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B5" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="39"/>
+      <c r="J5" s="39"/>
+      <c r="K5" s="39"/>
+      <c r="L5" s="39"/>
+      <c r="M5" s="40"/>
+    </row>
+    <row r="6" spans="2:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="39"/>
+      <c r="L6" s="39"/>
+      <c r="M6" s="40"/>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B7" s="46"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="39"/>
+      <c r="K7" s="39"/>
+      <c r="L7" s="39"/>
+      <c r="M7" s="40"/>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B8" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="39"/>
+      <c r="K8" s="39"/>
+      <c r="L8" s="39"/>
+      <c r="M8" s="40"/>
+    </row>
+    <row r="9" spans="2:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="39"/>
+      <c r="J9" s="39"/>
+      <c r="K9" s="39"/>
+      <c r="L9" s="39"/>
+      <c r="M9" s="40"/>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B10" s="47"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="39"/>
+      <c r="K10" s="39"/>
+      <c r="L10" s="39"/>
+      <c r="M10" s="40"/>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B11" s="47"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="39"/>
+      <c r="I11" s="39"/>
+      <c r="J11" s="39"/>
+      <c r="K11" s="39"/>
+      <c r="L11" s="39"/>
+      <c r="M11" s="40"/>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B12" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="38"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="39"/>
+      <c r="K12" s="39"/>
+      <c r="L12" s="39"/>
+      <c r="M12" s="40"/>
+    </row>
+    <row r="13" spans="2:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="48"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="48"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="39"/>
+      <c r="L13" s="39"/>
+      <c r="M13" s="40"/>
+    </row>
+    <row r="14" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B14" s="49"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="50"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="41"/>
+      <c r="K14" s="41"/>
+      <c r="L14" s="41"/>
+      <c r="M14" s="42"/>
+    </row>
+    <row r="15" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B15" s="51"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="51"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="51"/>
+      <c r="K15" s="51"/>
+      <c r="L15" s="51"/>
+      <c r="M15" s="51"/>
+    </row>
+    <row r="16" spans="2:13" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="21"/>
+    </row>
+    <row r="17" spans="2:13" ht="19.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B17" s="22"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="23"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="23"/>
+      <c r="L17" s="23"/>
+      <c r="M17" s="24"/>
+    </row>
+    <row r="18" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B18" s="51"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="51"/>
+      <c r="F18" s="51"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="51"/>
+      <c r="J18" s="51"/>
+      <c r="K18" s="51"/>
+      <c r="L18" s="51"/>
+      <c r="M18" s="51"/>
+    </row>
+    <row r="19" spans="2:13" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B19" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="26"/>
+      <c r="K19" s="26"/>
+      <c r="L19" s="26"/>
+      <c r="M19" s="27"/>
     </row>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B2" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B20" s="28"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="29"/>
+      <c r="K20" s="29"/>
+      <c r="L20" s="29"/>
+      <c r="M20" s="30"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="18"/>
-      <c r="M3" s="18"/>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B21" s="28"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="29"/>
+      <c r="I21" s="29"/>
+      <c r="J21" s="29"/>
+      <c r="K21" s="29"/>
+      <c r="L21" s="29"/>
+      <c r="M21" s="30"/>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B22" s="28"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="29"/>
+      <c r="I22" s="29"/>
+      <c r="J22" s="29"/>
+      <c r="K22" s="29"/>
+      <c r="L22" s="29"/>
+      <c r="M22" s="30"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B5" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="18"/>
-      <c r="L5" s="18"/>
-      <c r="M5" s="18"/>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B23" s="28"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="29"/>
+      <c r="K23" s="29"/>
+      <c r="L23" s="29"/>
+      <c r="M23" s="30"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="18"/>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B24" s="28"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="29"/>
+      <c r="H24" s="29"/>
+      <c r="I24" s="29"/>
+      <c r="J24" s="29"/>
+      <c r="K24" s="29"/>
+      <c r="L24" s="29"/>
+      <c r="M24" s="30"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="18"/>
-      <c r="L7" s="18"/>
-      <c r="M7" s="18"/>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B25" s="28"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="29"/>
+      <c r="K25" s="29"/>
+      <c r="L25" s="29"/>
+      <c r="M25" s="30"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B8" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="18"/>
-      <c r="L8" s="18"/>
-      <c r="M8" s="18"/>
+    <row r="26" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B26" s="28"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29"/>
+      <c r="K26" s="29"/>
+      <c r="L26" s="29"/>
+      <c r="M26" s="30"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="18"/>
-      <c r="L9" s="18"/>
-      <c r="M9" s="18"/>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B27" s="28"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="29"/>
+      <c r="K27" s="29"/>
+      <c r="L27" s="29"/>
+      <c r="M27" s="30"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="18"/>
-      <c r="K10" s="18"/>
-      <c r="L10" s="18"/>
-      <c r="M10" s="18"/>
+    <row r="28" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B28" s="28"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="29"/>
+      <c r="K28" s="29"/>
+      <c r="L28" s="29"/>
+      <c r="M28" s="30"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="18"/>
-      <c r="M11" s="18"/>
+    <row r="29" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B29" s="28"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="29"/>
+      <c r="L29" s="29"/>
+      <c r="M29" s="30"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B12" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="18"/>
-      <c r="L12" s="18"/>
-      <c r="M12" s="18"/>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B30" s="28"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="29"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="29"/>
+      <c r="K30" s="29"/>
+      <c r="L30" s="29"/>
+      <c r="M30" s="30"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="18"/>
-      <c r="K13" s="18"/>
-      <c r="L13" s="18"/>
-      <c r="M13" s="18"/>
+    <row r="31" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B31" s="28"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29"/>
+      <c r="I31" s="29"/>
+      <c r="J31" s="29"/>
+      <c r="K31" s="29"/>
+      <c r="L31" s="29"/>
+      <c r="M31" s="30"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="18"/>
-      <c r="K14" s="18"/>
-      <c r="L14" s="18"/>
-      <c r="M14" s="18"/>
+    <row r="32" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B32" s="28"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29"/>
+      <c r="K32" s="29"/>
+      <c r="L32" s="29"/>
+      <c r="M32" s="30"/>
     </row>
-    <row r="16" spans="2:13" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
-      <c r="M16" s="19"/>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B33" s="28"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="29"/>
+      <c r="I33" s="29"/>
+      <c r="J33" s="29"/>
+      <c r="K33" s="29"/>
+      <c r="L33" s="29"/>
+      <c r="M33" s="30"/>
     </row>
-    <row r="17" spans="2:13" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="19"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="19"/>
-      <c r="M17" s="19"/>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B34" s="28"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="29"/>
+      <c r="E34" s="29"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="29"/>
+      <c r="H34" s="29"/>
+      <c r="I34" s="29"/>
+      <c r="J34" s="29"/>
+      <c r="K34" s="29"/>
+      <c r="L34" s="29"/>
+      <c r="M34" s="30"/>
     </row>
-    <row r="19" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B19" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-    </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="16"/>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-    </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-    </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="16"/>
-      <c r="J22" s="16"/>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-    </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-    </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-    </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-    </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16"/>
-      <c r="J26" s="16"/>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-    </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="16"/>
-      <c r="J27" s="16"/>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-    </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="16"/>
-      <c r="J28" s="16"/>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-    </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B29" s="16"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="16"/>
-      <c r="I29" s="16"/>
-      <c r="J29" s="16"/>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-    </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B30" s="16"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
-      <c r="H30" s="16"/>
-      <c r="I30" s="16"/>
-      <c r="J30" s="16"/>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-    </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B31" s="16"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="16"/>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-    </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B32" s="16"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16"/>
-      <c r="I32" s="16"/>
-      <c r="J32" s="16"/>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B33" s="16"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="16"/>
-      <c r="H33" s="16"/>
-      <c r="I33" s="16"/>
-      <c r="J33" s="16"/>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B34" s="16"/>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="16"/>
-      <c r="I34" s="16"/>
-      <c r="J34" s="16"/>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B35" s="16"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16"/>
-      <c r="H35" s="16"/>
-      <c r="I35" s="16"/>
-      <c r="J35" s="16"/>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
+    <row r="35" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B35" s="31"/>
+      <c r="C35" s="32"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="32"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="32"/>
+      <c r="J35" s="32"/>
+      <c r="K35" s="32"/>
+      <c r="L35" s="32"/>
+      <c r="M35" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B16:M17"/>
+    <mergeCell ref="B19:M19"/>
+    <mergeCell ref="B20:M35"/>
     <mergeCell ref="B1:M1"/>
-    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="H2:M14"/>
     <mergeCell ref="B3:G4"/>
     <mergeCell ref="B5:G5"/>
     <mergeCell ref="B6:G7"/>
-    <mergeCell ref="B19:M19"/>
-    <mergeCell ref="B20:M35"/>
-    <mergeCell ref="B13:G14"/>
-    <mergeCell ref="H2:M14"/>
-    <mergeCell ref="B16:M17"/>
     <mergeCell ref="B8:G8"/>
     <mergeCell ref="B9:G11"/>
     <mergeCell ref="B12:G12"/>
+    <mergeCell ref="B13:G14"/>
+    <mergeCell ref="B2:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -17720,820 +18161,820 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95C33988-F7CE-4328-9503-C90086ACB249}">
   <dimension ref="A1:X31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="14" max="14" width="14.33203125" customWidth="1"/>
+    <col min="14" max="14" width="14.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+    <row r="1" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
+      <c r="S1" s="16"/>
+      <c r="T1" s="16"/>
+      <c r="U1" s="16"/>
+      <c r="V1" s="16"/>
+      <c r="W1" s="16"/>
+      <c r="X1" s="16"/>
+    </row>
+    <row r="2" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="16"/>
+      <c r="S2" s="16"/>
+      <c r="T2" s="16"/>
+      <c r="U2" s="16"/>
+      <c r="V2" s="16"/>
+      <c r="W2" s="16"/>
+      <c r="X2" s="16"/>
+    </row>
+    <row r="3" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="23"/>
-      <c r="O1" s="23"/>
-      <c r="P1" s="23"/>
-      <c r="Q1" s="23"/>
-      <c r="R1" s="23"/>
-      <c r="S1" s="23"/>
-      <c r="T1" s="23"/>
-      <c r="U1" s="23"/>
-      <c r="V1" s="23"/>
-      <c r="W1" s="23"/>
-      <c r="X1" s="23"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="18"/>
+      <c r="O3" s="18"/>
+      <c r="P3" s="18"/>
+      <c r="Q3" s="18"/>
+      <c r="R3" s="18"/>
+      <c r="S3" s="18"/>
+      <c r="T3" s="18"/>
+      <c r="U3" s="18"/>
+      <c r="V3" s="18"/>
+      <c r="W3" s="18"/>
+      <c r="X3" s="18"/>
     </row>
-    <row r="2" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="23"/>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="23"/>
-      <c r="L2" s="23"/>
-      <c r="M2" s="23"/>
-      <c r="N2" s="23"/>
-      <c r="O2" s="23"/>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23"/>
-      <c r="R2" s="23"/>
-      <c r="S2" s="23"/>
-      <c r="T2" s="23"/>
-      <c r="U2" s="23"/>
-      <c r="V2" s="23"/>
-      <c r="W2" s="23"/>
-      <c r="X2" s="23"/>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="18"/>
+      <c r="O4" s="18"/>
+      <c r="P4" s="18"/>
+      <c r="Q4" s="18"/>
+      <c r="R4" s="18"/>
+      <c r="S4" s="18"/>
+      <c r="T4" s="18"/>
+      <c r="U4" s="18"/>
+      <c r="V4" s="18"/>
+      <c r="W4" s="18"/>
+      <c r="X4" s="18"/>
     </row>
-    <row r="3" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="25"/>
-      <c r="R3" s="25"/>
-      <c r="S3" s="25"/>
-      <c r="T3" s="25"/>
-      <c r="U3" s="25"/>
-      <c r="V3" s="25"/>
-      <c r="W3" s="25"/>
-      <c r="X3" s="25"/>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A5" s="17"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="18"/>
+      <c r="M5" s="18"/>
+      <c r="N5" s="18"/>
+      <c r="O5" s="18"/>
+      <c r="P5" s="18"/>
+      <c r="Q5" s="18"/>
+      <c r="R5" s="18"/>
+      <c r="S5" s="18"/>
+      <c r="T5" s="18"/>
+      <c r="U5" s="18"/>
+      <c r="V5" s="18"/>
+      <c r="W5" s="18"/>
+      <c r="X5" s="18"/>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A4" s="24"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="25"/>
-      <c r="O4" s="25"/>
-      <c r="P4" s="25"/>
-      <c r="Q4" s="25"/>
-      <c r="R4" s="25"/>
-      <c r="S4" s="25"/>
-      <c r="T4" s="25"/>
-      <c r="U4" s="25"/>
-      <c r="V4" s="25"/>
-      <c r="W4" s="25"/>
-      <c r="X4" s="25"/>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
+      <c r="Q6" s="8"/>
+      <c r="R6" s="8"/>
+      <c r="S6" s="8"/>
+      <c r="T6" s="8"/>
+      <c r="U6" s="8"/>
+      <c r="V6" s="8"/>
+      <c r="W6" s="8"/>
+      <c r="X6" s="8"/>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A5" s="24"/>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="25"/>
-      <c r="M5" s="25"/>
-      <c r="N5" s="25"/>
-      <c r="O5" s="25"/>
-      <c r="P5" s="25"/>
-      <c r="Q5" s="25"/>
-      <c r="R5" s="25"/>
-      <c r="S5" s="25"/>
-      <c r="T5" s="25"/>
-      <c r="U5" s="25"/>
-      <c r="V5" s="25"/>
-      <c r="W5" s="25"/>
-      <c r="X5" s="25"/>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="8"/>
+      <c r="T7" s="8"/>
+      <c r="U7" s="8"/>
+      <c r="V7" s="8"/>
+      <c r="W7" s="8"/>
+      <c r="X7" s="8"/>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="16"/>
-      <c r="S6" s="16"/>
-      <c r="T6" s="16"/>
-      <c r="U6" s="16"/>
-      <c r="V6" s="16"/>
-      <c r="W6" s="16"/>
-      <c r="X6" s="16"/>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="8"/>
+      <c r="T8" s="8"/>
+      <c r="U8" s="8"/>
+      <c r="V8" s="8"/>
+      <c r="W8" s="8"/>
+      <c r="X8" s="8"/>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A7" s="16"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="16"/>
-      <c r="O7" s="16"/>
-      <c r="P7" s="16"/>
-      <c r="Q7" s="16"/>
-      <c r="R7" s="16"/>
-      <c r="S7" s="16"/>
-      <c r="T7" s="16"/>
-      <c r="U7" s="16"/>
-      <c r="V7" s="16"/>
-      <c r="W7" s="16"/>
-      <c r="X7" s="16"/>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
+      <c r="S9" s="8"/>
+      <c r="T9" s="8"/>
+      <c r="U9" s="8"/>
+      <c r="V9" s="8"/>
+      <c r="W9" s="8"/>
+      <c r="X9" s="8"/>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A8" s="16"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="16"/>
-      <c r="O8" s="16"/>
-      <c r="P8" s="16"/>
-      <c r="Q8" s="16"/>
-      <c r="R8" s="16"/>
-      <c r="S8" s="16"/>
-      <c r="T8" s="16"/>
-      <c r="U8" s="16"/>
-      <c r="V8" s="16"/>
-      <c r="W8" s="16"/>
-      <c r="X8" s="16"/>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="8"/>
+      <c r="T10" s="8"/>
+      <c r="U10" s="8"/>
+      <c r="V10" s="8"/>
+      <c r="W10" s="8"/>
+      <c r="X10" s="8"/>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A9" s="16"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="16"/>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="16"/>
-      <c r="R9" s="16"/>
-      <c r="S9" s="16"/>
-      <c r="T9" s="16"/>
-      <c r="U9" s="16"/>
-      <c r="V9" s="16"/>
-      <c r="W9" s="16"/>
-      <c r="X9" s="16"/>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+      <c r="Q11" s="8"/>
+      <c r="R11" s="8"/>
+      <c r="S11" s="8"/>
+      <c r="T11" s="8"/>
+      <c r="U11" s="8"/>
+      <c r="V11" s="8"/>
+      <c r="W11" s="8"/>
+      <c r="X11" s="8"/>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A10" s="16"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="16"/>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="16"/>
-      <c r="R10" s="16"/>
-      <c r="S10" s="16"/>
-      <c r="T10" s="16"/>
-      <c r="U10" s="16"/>
-      <c r="V10" s="16"/>
-      <c r="W10" s="16"/>
-      <c r="X10" s="16"/>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
+      <c r="R12" s="8"/>
+      <c r="S12" s="8"/>
+      <c r="T12" s="8"/>
+      <c r="U12" s="8"/>
+      <c r="V12" s="8"/>
+      <c r="W12" s="8"/>
+      <c r="X12" s="8"/>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A11" s="16"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="16"/>
-      <c r="O11" s="16"/>
-      <c r="P11" s="16"/>
-      <c r="Q11" s="16"/>
-      <c r="R11" s="16"/>
-      <c r="S11" s="16"/>
-      <c r="T11" s="16"/>
-      <c r="U11" s="16"/>
-      <c r="V11" s="16"/>
-      <c r="W11" s="16"/>
-      <c r="X11" s="16"/>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
+      <c r="Q13" s="8"/>
+      <c r="R13" s="8"/>
+      <c r="S13" s="8"/>
+      <c r="T13" s="8"/>
+      <c r="U13" s="8"/>
+      <c r="V13" s="8"/>
+      <c r="W13" s="8"/>
+      <c r="X13" s="8"/>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A12" s="16"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
-      <c r="O12" s="16"/>
-      <c r="P12" s="16"/>
-      <c r="Q12" s="16"/>
-      <c r="R12" s="16"/>
-      <c r="S12" s="16"/>
-      <c r="T12" s="16"/>
-      <c r="U12" s="16"/>
-      <c r="V12" s="16"/>
-      <c r="W12" s="16"/>
-      <c r="X12" s="16"/>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
+      <c r="Q14" s="8"/>
+      <c r="R14" s="8"/>
+      <c r="S14" s="8"/>
+      <c r="T14" s="8"/>
+      <c r="U14" s="8"/>
+      <c r="V14" s="8"/>
+      <c r="W14" s="8"/>
+      <c r="X14" s="8"/>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="16"/>
-      <c r="O13" s="16"/>
-      <c r="P13" s="16"/>
-      <c r="Q13" s="16"/>
-      <c r="R13" s="16"/>
-      <c r="S13" s="16"/>
-      <c r="T13" s="16"/>
-      <c r="U13" s="16"/>
-      <c r="V13" s="16"/>
-      <c r="W13" s="16"/>
-      <c r="X13" s="16"/>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8"/>
+      <c r="Q15" s="8"/>
+      <c r="R15" s="8"/>
+      <c r="S15" s="8"/>
+      <c r="T15" s="8"/>
+      <c r="U15" s="8"/>
+      <c r="V15" s="8"/>
+      <c r="W15" s="8"/>
+      <c r="X15" s="8"/>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="16"/>
-      <c r="O14" s="16"/>
-      <c r="P14" s="16"/>
-      <c r="Q14" s="16"/>
-      <c r="R14" s="16"/>
-      <c r="S14" s="16"/>
-      <c r="T14" s="16"/>
-      <c r="U14" s="16"/>
-      <c r="V14" s="16"/>
-      <c r="W14" s="16"/>
-      <c r="X14" s="16"/>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
+      <c r="R16" s="8"/>
+      <c r="S16" s="8"/>
+      <c r="T16" s="8"/>
+      <c r="U16" s="8"/>
+      <c r="V16" s="8"/>
+      <c r="W16" s="8"/>
+      <c r="X16" s="8"/>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A15" s="16"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="16"/>
-      <c r="O15" s="16"/>
-      <c r="P15" s="16"/>
-      <c r="Q15" s="16"/>
-      <c r="R15" s="16"/>
-      <c r="S15" s="16"/>
-      <c r="T15" s="16"/>
-      <c r="U15" s="16"/>
-      <c r="V15" s="16"/>
-      <c r="W15" s="16"/>
-      <c r="X15" s="16"/>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8"/>
+      <c r="Q17" s="8"/>
+      <c r="R17" s="8"/>
+      <c r="S17" s="8"/>
+      <c r="T17" s="8"/>
+      <c r="U17" s="8"/>
+      <c r="V17" s="8"/>
+      <c r="W17" s="8"/>
+      <c r="X17" s="8"/>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A16" s="16"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="16"/>
-      <c r="O16" s="16"/>
-      <c r="P16" s="16"/>
-      <c r="Q16" s="16"/>
-      <c r="R16" s="16"/>
-      <c r="S16" s="16"/>
-      <c r="T16" s="16"/>
-      <c r="U16" s="16"/>
-      <c r="V16" s="16"/>
-      <c r="W16" s="16"/>
-      <c r="X16" s="16"/>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="8"/>
+      <c r="Q18" s="8"/>
+      <c r="R18" s="8"/>
+      <c r="S18" s="8"/>
+      <c r="T18" s="8"/>
+      <c r="U18" s="8"/>
+      <c r="V18" s="8"/>
+      <c r="W18" s="8"/>
+      <c r="X18" s="8"/>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A17" s="16"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="16"/>
-      <c r="O17" s="16"/>
-      <c r="P17" s="16"/>
-      <c r="Q17" s="16"/>
-      <c r="R17" s="16"/>
-      <c r="S17" s="16"/>
-      <c r="T17" s="16"/>
-      <c r="U17" s="16"/>
-      <c r="V17" s="16"/>
-      <c r="W17" s="16"/>
-      <c r="X17" s="16"/>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="8"/>
+      <c r="Q19" s="8"/>
+      <c r="R19" s="8"/>
+      <c r="S19" s="8"/>
+      <c r="T19" s="8"/>
+      <c r="U19" s="8"/>
+      <c r="V19" s="8"/>
+      <c r="W19" s="8"/>
+      <c r="X19" s="8"/>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A18" s="16"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="16"/>
-      <c r="O18" s="16"/>
-      <c r="P18" s="16"/>
-      <c r="Q18" s="16"/>
-      <c r="R18" s="16"/>
-      <c r="S18" s="16"/>
-      <c r="T18" s="16"/>
-      <c r="U18" s="16"/>
-      <c r="V18" s="16"/>
-      <c r="W18" s="16"/>
-      <c r="X18" s="16"/>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="8"/>
+      <c r="Q20" s="8"/>
+      <c r="R20" s="8"/>
+      <c r="S20" s="8"/>
+      <c r="T20" s="8"/>
+      <c r="U20" s="8"/>
+      <c r="V20" s="8"/>
+      <c r="W20" s="8"/>
+      <c r="X20" s="8"/>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A19" s="16"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="16"/>
-      <c r="O19" s="16"/>
-      <c r="P19" s="16"/>
-      <c r="Q19" s="16"/>
-      <c r="R19" s="16"/>
-      <c r="S19" s="16"/>
-      <c r="T19" s="16"/>
-      <c r="U19" s="16"/>
-      <c r="V19" s="16"/>
-      <c r="W19" s="16"/>
-      <c r="X19" s="16"/>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="8"/>
+      <c r="Q21" s="8"/>
+      <c r="R21" s="8"/>
+      <c r="S21" s="8"/>
+      <c r="T21" s="8"/>
+      <c r="U21" s="8"/>
+      <c r="V21" s="8"/>
+      <c r="W21" s="8"/>
+      <c r="X21" s="8"/>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A20" s="16"/>
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="16"/>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="16"/>
-      <c r="O20" s="16"/>
-      <c r="P20" s="16"/>
-      <c r="Q20" s="16"/>
-      <c r="R20" s="16"/>
-      <c r="S20" s="16"/>
-      <c r="T20" s="16"/>
-      <c r="U20" s="16"/>
-      <c r="V20" s="16"/>
-      <c r="W20" s="16"/>
-      <c r="X20" s="16"/>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="8"/>
+      <c r="Q22" s="8"/>
+      <c r="R22" s="8"/>
+      <c r="S22" s="8"/>
+      <c r="T22" s="8"/>
+      <c r="U22" s="8"/>
+      <c r="V22" s="8"/>
+      <c r="W22" s="8"/>
+      <c r="X22" s="8"/>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A21" s="16"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="16"/>
-      <c r="O21" s="16"/>
-      <c r="P21" s="16"/>
-      <c r="Q21" s="16"/>
-      <c r="R21" s="16"/>
-      <c r="S21" s="16"/>
-      <c r="T21" s="16"/>
-      <c r="U21" s="16"/>
-      <c r="V21" s="16"/>
-      <c r="W21" s="16"/>
-      <c r="X21" s="16"/>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
+      <c r="P23" s="8"/>
+      <c r="Q23" s="8"/>
+      <c r="R23" s="8"/>
+      <c r="S23" s="8"/>
+      <c r="T23" s="8"/>
+      <c r="U23" s="8"/>
+      <c r="V23" s="8"/>
+      <c r="W23" s="8"/>
+      <c r="X23" s="8"/>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A22" s="16"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="16"/>
-      <c r="J22" s="16"/>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="16"/>
-      <c r="O22" s="16"/>
-      <c r="P22" s="16"/>
-      <c r="Q22" s="16"/>
-      <c r="R22" s="16"/>
-      <c r="S22" s="16"/>
-      <c r="T22" s="16"/>
-      <c r="U22" s="16"/>
-      <c r="V22" s="16"/>
-      <c r="W22" s="16"/>
-      <c r="X22" s="16"/>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8"/>
+      <c r="Q24" s="8"/>
+      <c r="R24" s="8"/>
+      <c r="S24" s="8"/>
+      <c r="T24" s="8"/>
+      <c r="U24" s="8"/>
+      <c r="V24" s="8"/>
+      <c r="W24" s="8"/>
+      <c r="X24" s="8"/>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A23" s="16"/>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="16"/>
-      <c r="O23" s="16"/>
-      <c r="P23" s="16"/>
-      <c r="Q23" s="16"/>
-      <c r="R23" s="16"/>
-      <c r="S23" s="16"/>
-      <c r="T23" s="16"/>
-      <c r="U23" s="16"/>
-      <c r="V23" s="16"/>
-      <c r="W23" s="16"/>
-      <c r="X23" s="16"/>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
+      <c r="O25" s="8"/>
+      <c r="P25" s="8"/>
+      <c r="Q25" s="8"/>
+      <c r="R25" s="8"/>
+      <c r="S25" s="8"/>
+      <c r="T25" s="8"/>
+      <c r="U25" s="8"/>
+      <c r="V25" s="8"/>
+      <c r="W25" s="8"/>
+      <c r="X25" s="8"/>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A24" s="16"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="16"/>
-      <c r="O24" s="16"/>
-      <c r="P24" s="16"/>
-      <c r="Q24" s="16"/>
-      <c r="R24" s="16"/>
-      <c r="S24" s="16"/>
-      <c r="T24" s="16"/>
-      <c r="U24" s="16"/>
-      <c r="V24" s="16"/>
-      <c r="W24" s="16"/>
-      <c r="X24" s="16"/>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8"/>
+      <c r="O26" s="8"/>
+      <c r="P26" s="8"/>
+      <c r="Q26" s="8"/>
+      <c r="R26" s="8"/>
+      <c r="S26" s="8"/>
+      <c r="T26" s="8"/>
+      <c r="U26" s="8"/>
+      <c r="V26" s="8"/>
+      <c r="W26" s="8"/>
+      <c r="X26" s="8"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A25" s="16"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="16"/>
-      <c r="O25" s="16"/>
-      <c r="P25" s="16"/>
-      <c r="Q25" s="16"/>
-      <c r="R25" s="16"/>
-      <c r="S25" s="16"/>
-      <c r="T25" s="16"/>
-      <c r="U25" s="16"/>
-      <c r="V25" s="16"/>
-      <c r="W25" s="16"/>
-      <c r="X25" s="16"/>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="N27" s="8"/>
+      <c r="O27" s="8"/>
+      <c r="P27" s="8"/>
+      <c r="Q27" s="8"/>
+      <c r="R27" s="8"/>
+      <c r="S27" s="8"/>
+      <c r="T27" s="8"/>
+      <c r="U27" s="8"/>
+      <c r="V27" s="8"/>
+      <c r="W27" s="8"/>
+      <c r="X27" s="8"/>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A26" s="16"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16"/>
-      <c r="J26" s="16"/>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="16"/>
-      <c r="O26" s="16"/>
-      <c r="P26" s="16"/>
-      <c r="Q26" s="16"/>
-      <c r="R26" s="16"/>
-      <c r="S26" s="16"/>
-      <c r="T26" s="16"/>
-      <c r="U26" s="16"/>
-      <c r="V26" s="16"/>
-      <c r="W26" s="16"/>
-      <c r="X26" s="16"/>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="8"/>
+      <c r="P28" s="8"/>
+      <c r="Q28" s="8"/>
+      <c r="R28" s="8"/>
+      <c r="S28" s="8"/>
+      <c r="T28" s="8"/>
+      <c r="U28" s="8"/>
+      <c r="V28" s="8"/>
+      <c r="W28" s="8"/>
+      <c r="X28" s="8"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A27" s="16"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="16"/>
-      <c r="J27" s="16"/>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="16"/>
-      <c r="O27" s="16"/>
-      <c r="P27" s="16"/>
-      <c r="Q27" s="16"/>
-      <c r="R27" s="16"/>
-      <c r="S27" s="16"/>
-      <c r="T27" s="16"/>
-      <c r="U27" s="16"/>
-      <c r="V27" s="16"/>
-      <c r="W27" s="16"/>
-      <c r="X27" s="16"/>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
+      <c r="N29" s="8"/>
+      <c r="O29" s="8"/>
+      <c r="P29" s="8"/>
+      <c r="Q29" s="8"/>
+      <c r="R29" s="8"/>
+      <c r="S29" s="8"/>
+      <c r="T29" s="8"/>
+      <c r="U29" s="8"/>
+      <c r="V29" s="8"/>
+      <c r="W29" s="8"/>
+      <c r="X29" s="8"/>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A28" s="16"/>
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="16"/>
-      <c r="J28" s="16"/>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="16"/>
-      <c r="O28" s="16"/>
-      <c r="P28" s="16"/>
-      <c r="Q28" s="16"/>
-      <c r="R28" s="16"/>
-      <c r="S28" s="16"/>
-      <c r="T28" s="16"/>
-      <c r="U28" s="16"/>
-      <c r="V28" s="16"/>
-      <c r="W28" s="16"/>
-      <c r="X28" s="16"/>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="8"/>
+      <c r="O30" s="8"/>
+      <c r="P30" s="8"/>
+      <c r="Q30" s="8"/>
+      <c r="R30" s="8"/>
+      <c r="S30" s="8"/>
+      <c r="T30" s="8"/>
+      <c r="U30" s="8"/>
+      <c r="V30" s="8"/>
+      <c r="W30" s="8"/>
+      <c r="X30" s="8"/>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A29" s="16"/>
-      <c r="B29" s="16"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="16"/>
-      <c r="I29" s="16"/>
-      <c r="J29" s="16"/>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="16"/>
-      <c r="O29" s="16"/>
-      <c r="P29" s="16"/>
-      <c r="Q29" s="16"/>
-      <c r="R29" s="16"/>
-      <c r="S29" s="16"/>
-      <c r="T29" s="16"/>
-      <c r="U29" s="16"/>
-      <c r="V29" s="16"/>
-      <c r="W29" s="16"/>
-      <c r="X29" s="16"/>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A30" s="16"/>
-      <c r="B30" s="16"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
-      <c r="H30" s="16"/>
-      <c r="I30" s="16"/>
-      <c r="J30" s="16"/>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="16"/>
-      <c r="O30" s="16"/>
-      <c r="P30" s="16"/>
-      <c r="Q30" s="16"/>
-      <c r="R30" s="16"/>
-      <c r="S30" s="16"/>
-      <c r="T30" s="16"/>
-      <c r="U30" s="16"/>
-      <c r="V30" s="16"/>
-      <c r="W30" s="16"/>
-      <c r="X30" s="16"/>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A31" s="16"/>
-      <c r="B31" s="16"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="16"/>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="16"/>
-      <c r="O31" s="16"/>
-      <c r="P31" s="16"/>
-      <c r="Q31" s="16"/>
-      <c r="R31" s="16"/>
-      <c r="S31" s="16"/>
-      <c r="T31" s="16"/>
-      <c r="U31" s="16"/>
-      <c r="V31" s="16"/>
-      <c r="W31" s="16"/>
-      <c r="X31" s="16"/>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="8"/>
+      <c r="K31" s="8"/>
+      <c r="L31" s="8"/>
+      <c r="M31" s="8"/>
+      <c r="N31" s="8"/>
+      <c r="O31" s="8"/>
+      <c r="P31" s="8"/>
+      <c r="Q31" s="8"/>
+      <c r="R31" s="8"/>
+      <c r="S31" s="8"/>
+      <c r="T31" s="8"/>
+      <c r="U31" s="8"/>
+      <c r="V31" s="8"/>
+      <c r="W31" s="8"/>
+      <c r="X31" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">
